--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N95_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.06446971229579</v>
+        <v>4.885476328248066</v>
       </c>
       <c r="D2" t="n">
-        <v>30.31074251269681</v>
+        <v>4.925495658313231</v>
       </c>
       <c r="E2" t="n">
-        <v>4.083386252805587</v>
+        <v>0.6635502660809078</v>
       </c>
       <c r="F2" t="n">
-        <v>3.865066025599958</v>
+        <v>0.6280732291599933</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.89769720668462</v>
+        <v>3.55837579608625</v>
       </c>
       <c r="D3" t="n">
-        <v>22.58061046149689</v>
+        <v>3.669349199993245</v>
       </c>
       <c r="E3" t="n">
-        <v>4.083386252805587</v>
+        <v>0.6635502660809078</v>
       </c>
       <c r="F3" t="n">
-        <v>3.865066025599958</v>
+        <v>0.6280732291599933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
